--- a/docs/risk/Risk Register/Risk Register V0.9.xlsx
+++ b/docs/risk/Risk Register/Risk Register V0.9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elind\m4-wt\records\docs\risk\Risk Register\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB99E6F7-B41A-413B-A857-572C4BB4804C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C341170-B9AF-4184-81F8-E6C28839C22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="249">
   <si>
     <t>8.3 Highest-priority risk — defence</t>
   </si>
@@ -671,9 +671,6 @@
     <t>Move production to the lowest paid tier through controlled change (cost recorded against STK-008 under CON-003).</t>
   </si>
   <si>
-    <t>Open — reviewed at M3</t>
-  </si>
-  <si>
     <t>DEC-010 · DEC-003 · NFR-2.1 · NFR-2.4 · CON-010 · OI-10 · DEC-003 v0.4 · docs/evidence/M3_Staging_Deploy_v3.0-M3-rc.md (section 8) · docs/evidence/M3-perf/NFR-2.4_load_run_2026-10-15.txt</t>
   </si>
   <si>
@@ -749,36 +746,19 @@
     <t>Unchanged score, now load-bearing. DEC-012 enforcement point 3 (field-level serialiser) rests on the CFL-002 resolution, still Proposed (condition C-01 open). PR #62 review B-1 found security-category requests could not be closed or rejected by anyone; fixed there by giving the Security Officer disposition rights, recorded for confirmation under OI-15. M4 review, 17/10/2026: unchanged and still a go-live blocker: DEC-012 point 3 is not built, AC-FR-1.5 is Partial (OI-16, OI-17), and the whole read of a security-category request is refused to staff who are not Security Officers. DEF-024 (S1, a per-viewer response reused from the browser cache) was this risk materialising in the client; it is fixed and E2E-10 covers it.</t>
   </si>
   <si>
-    <t>Reviewed at M2 — no change. M4 review, 17/10/2026: pending the RC performance runs on staging (NFR-2.1, NFR-2.4); NFR-2.2, NFR-2.3 and NFR-2.5 were not measured.</t>
-  </si>
-  <si>
     <t>Reviewed at M2 — no change. M4 review, 17/10/2026: mitigated: every Requester and Technician screen and interaction is measured at 360 px in four browsers (E2E-6, E2E-13: no page scroll, no sideways-scrolling control, every control at least 44 x 44), after the queue was laid out as cards on phones (1691e0f).</t>
   </si>
   <si>
-    <t>Mitigated, not closed. DEC-011 accepted that no single location states what a transition does; bounded by the single subscription registry (src/events/subscribers/index.js, listSubscriptions() asserted by test). RTM extended to v0.5; the pull request template (#53) will require the affected IDs. Residual: a merged change that skips the RTM update. M4 review, 17/10/2026: mitigation continued: RTM v0.11 is updated from the M4 build and the evidence runs [pending: RTM v0.11 PR].</t>
-  </si>
-  <si>
-    <t>Observed at M2: pull requests #61 and #62 were reviewed by both other members on the same day, with written review records. Review turnaround is holding; small single-purpose pull requests remain the mitigation. M4 review, 17/10/2026: observed again: every M4 PR needs two approvals from the other members, and the integration PR #136 waits on them before the RC [update when merged].</t>
-  </si>
-  <si>
     <t>Materialised, not avoided. DEC-002 and DEC-003 closed on 29/09/2026, after the 22/09/2026 working deadline; the consequence is recorded against conditions C-04 and C-05 (Appendix B). Row retained as a record of the realised risk; no further mitigation applies. M4 review, 17/10/2026: materialised at M2; no change.</t>
   </si>
   <si>
     <t>New at M2 — raised by the architecture baseline (PED §6A.9, DEC-014). M4 review, 17/10/2026: no erosion found: the CI layer check (a step of the Build and test job: no route or middleware imports a model or repository) passes on PR #136.</t>
   </si>
   <si>
-    <t>New at M2 — raised by the architecture baseline (PED §6A.9, DEC-014). M4 review, 17/10/2026: pending the RC staging runs; availability over a month is not measurable in M4 (AC-NFR-2.5 Not Met).</t>
-  </si>
-  <si>
     <t>New at M2 — raised by the data and technology baseline (PED §6B/§6C, DEC-016). M4 review, 17/10/2026: the trigger is defined (scripts/atlas/app/) but not deployed on either cluster, so there is no trigger-written audit to suspend: AC-NFR-1.9 is Not Met and AC-NFR-1.10 v0.3's auditLog clauses are not shown. The exposure is the trigger's absence, not its suspension.</t>
   </si>
   <si>
     <t>New at M2 — raised by DEC-010 (PED §10.8). M4 review, 17/10/2026: no change; no backup has run (DEC-010), AC-NFR-1.5 Not Met.</t>
-  </si>
-  <si>
-    <t>New at M2 — raised by DEC-010 (PED §6C, §10.8). 
-M3 review, 16/10/2026: observed in the NFR-2.4 load run on staging (15/10/2026, release candidate v3.0-M3-rc, staging cluster civicconnectstaging, M0). 100 concurrent authenticated users for 600 s: 100 logins during the ramp, then 5,835 reads and 900 status transitions in the window (11.04 requests/s), with 0 failed requests and 0 unhandled server errors. The early-warning indicator was not read: the Atlas metrics for 16:30 to 16:42 UTC were not captured, so database load is an estimate of about 40 to 50 ops/s (data baseline s.7 arithmetic), not a measurement against the 70 ops/s trigger. Storage was not checked. Score unchanged (2 × 2): the run is consistent with the estimate but does not measure the ceiling. Context changed: DEC-003 v0.4 leaves production infrastructure undecided, so the free cluster in production is no longer settled; the risk applies to staging now and to production once its cluster is chosen. Next action: capture Atlas operation and storage metrics during the next load run.
-M4 review, 17/10/2026: pending the RC performance runs on staging (NFR-2.4 load run and NFR-2.1 submission timing).</t>
   </si>
   <si>
     <t>New at M3 — raised by DEC-018 (11/10/2026). Scored P2 × I3 = 6 (High) by the owner, consistent with RSK-009 and RSK-016, the same class of risk. P2: the risk rests on an unconfirmed assumption, that the slow hash caps the guess rate, which has not been measured. Not P3: CON-019 adversarial testing is planned, not an indicator already present.
@@ -790,6 +770,29 @@
   </si>
   <si>
     <t>Open — trigger not deployed (M4)</t>
+  </si>
+  <si>
+    <t>Open — partly materialised at M4</t>
+  </si>
+  <si>
+    <t>Open — indicator reached at M4 (partly materialised)</t>
+  </si>
+  <si>
+    <t>Reviewed at M2 — no change. M4 review, 17/10/2026: at the RC on staging (18/10/2026, docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md) NFR-2.4 failed (17 submission timeouts under 100 users, 0 server errors) and NFR-2.1 was not met (2 of 100 submissions confirmed within 3 s, 30 lost): the thresholds were not achieved on the M0 cluster, not colocated with the VM, with the per-year reference counter contended (DEF-032). NFR-2.2, NFR-2.3 and NFR-2.5 were not measured. Partly materialised.</t>
+  </si>
+  <si>
+    <t>Mitigated, not closed. DEC-011 accepted that no single location states what a transition does; bounded by the single subscription registry (src/events/subscribers/index.js, listSubscriptions() asserted by test). RTM extended to v0.5; the pull request template (#53) will require the affected IDs. Residual: a merged change that skips the RTM update. M4 review, 17/10/2026: mitigation continued: RTM v0.11 is updated from the M4 build and the evidence runs (RTM v0.11 in PR #139, including the rows evidenced on staging at the RC, 18/10/2026).</t>
+  </si>
+  <si>
+    <t>Observed at M2: pull requests #61 and #62 were reviewed by both other members on the same day, with written review records. Review turnaround is holding; small single-purpose pull requests remain the mitigation. M4 review, 17/10/2026: observed again: every M4 PR needs two approvals from the other members, and the integration PR #136 was approved by both (23:28 and 23:34 UTC on 17/10/2026) and merged at 23:34; the RC promotion PR #138 was approved by both and merged at 00:15 UTC on 18/10/2026. The rule held without stalling the RC.</t>
+  </si>
+  <si>
+    <t>New at M2 — raised by the architecture baseline (PED §6A.9, DEC-014). M4 review, 17/10/2026: the service stayed active through the RC staging session of 18/10/2026 (docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md), including two restarts (the deploy and the AC-NFR-2.7 check), and recovered after both load runs; availability over a month is not measurable in M4 (AC-NFR-2.5 Not Met).</t>
+  </si>
+  <si>
+    <t>New at M2 — raised by DEC-010 (PED §6C, §10.8). 
+M3 review, 16/10/2026: observed in the NFR-2.4 load run on staging (15/10/2026, release candidate v3.0-M3-rc, staging cluster civicconnectstaging, M0). 100 concurrent authenticated users for 600 s: 100 logins during the ramp, then 5,835 reads and 900 status transitions in the window (11.04 requests/s), with 0 failed requests and 0 unhandled server errors. The early-warning indicator was not read: the Atlas metrics for 16:30 to 16:42 UTC were not captured, so database load is an estimate of about 40 to 50 ops/s (data baseline s.7 arithmetic), not a measurement against the 70 ops/s trigger. Storage was not checked. Score unchanged (2 × 2): the run is consistent with the estimate but does not measure the ceiling. Context changed: DEC-003 v0.4 leaves production infrastructure undecided, so the free cluster in production is no longer settled; the risk applies to staging now and to production once its cluster is chosen. Next action: capture Atlas operation and storage metrics during the next load run.
+M4 review, 17/10/2026: pending the RC performance runs on staging (NFR-2.4 load run and NFR-2.1 submission timing). Result at the RC (18/10/2026, docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md): the early-warning indicator was reached. During the NFR-2.4 run Atlas reported about 74 ops/s (trigger 70; M0 limit 100) and connections rose from 3 to 53; every request type's tail grew against M3 (read p95 0.87 s against 0.25 s at about 1.8 times M3's request rate). With the per-year reference counter contended (DEF-032), submissions timed out or were lost: NFR-2.4 failed and NFR-2.1 was not met. Partly materialised; a paid or colocated tier is a go-live condition.</t>
   </si>
 </sst>
 </file>
@@ -1575,14 +1578,14 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1984,11 +1987,11 @@
       <c r="E19" s="30"/>
     </row>
     <row r="20" spans="2:5" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="77" t="s">
+      <c r="B20" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
       <c r="E20" s="30"/>
     </row>
     <row r="21" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -2074,11 +2077,11 @@
       <c r="E28" s="30"/>
     </row>
     <row r="29" spans="2:5" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="77" t="s">
+      <c r="B29" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="78"/>
-      <c r="D29" s="78"/>
+      <c r="C29" s="80"/>
+      <c r="D29" s="80"/>
       <c r="E29" s="30"/>
     </row>
     <row r="30" spans="2:5" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2256,10 +2259,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="80"/>
+      <c r="C1" s="78"/>
     </row>
     <row r="2" spans="2:16" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="27" t="s">
@@ -2349,7 +2352,7 @@
         <v>77</v>
       </c>
       <c r="O3" s="55" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P3" s="8"/>
     </row>
@@ -2396,7 +2399,7 @@
         <v>85</v>
       </c>
       <c r="O4" s="57" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P4" s="8"/>
     </row>
@@ -2443,7 +2446,7 @@
         <v>93</v>
       </c>
       <c r="O5" s="55" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P5" s="8"/>
     </row>
@@ -2490,7 +2493,7 @@
         <v>100</v>
       </c>
       <c r="O6" s="57" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P6" s="8"/>
     </row>
@@ -2537,7 +2540,7 @@
         <v>107</v>
       </c>
       <c r="O7" s="55" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P7" s="8"/>
     </row>
@@ -2584,7 +2587,7 @@
         <v>114</v>
       </c>
       <c r="O8" s="57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P8" s="8"/>
     </row>
@@ -2631,7 +2634,7 @@
         <v>121</v>
       </c>
       <c r="O9" s="55" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P9" s="8"/>
     </row>
@@ -2678,7 +2681,7 @@
         <v>129</v>
       </c>
       <c r="O10" s="57" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P10" s="8"/>
     </row>
@@ -2725,7 +2728,7 @@
         <v>136</v>
       </c>
       <c r="O11" s="55" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P11" s="8"/>
     </row>
@@ -2766,13 +2769,13 @@
         <v>92</v>
       </c>
       <c r="M12" s="70" t="s">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="N12" s="57" t="s">
         <v>143</v>
       </c>
       <c r="O12" s="57" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="P12" s="8"/>
     </row>
@@ -2813,13 +2816,13 @@
         <v>92</v>
       </c>
       <c r="M13" s="65" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="N13" s="55" t="s">
         <v>150</v>
       </c>
       <c r="O13" s="55" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P13" s="8"/>
     </row>
@@ -2866,7 +2869,7 @@
         <v>158</v>
       </c>
       <c r="O14" s="57" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="P14" s="8"/>
     </row>
@@ -2913,7 +2916,7 @@
         <v>166</v>
       </c>
       <c r="O15" s="55" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="P15" s="8"/>
     </row>
@@ -2960,7 +2963,7 @@
         <v>173</v>
       </c>
       <c r="O16" s="57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P16" s="8"/>
     </row>
@@ -3007,7 +3010,7 @@
         <v>181</v>
       </c>
       <c r="O17" s="59" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="P17" s="8"/>
     </row>
@@ -3054,7 +3057,7 @@
         <v>188</v>
       </c>
       <c r="O18" s="59" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="P18" s="8"/>
     </row>
@@ -3101,7 +3104,7 @@
         <v>195</v>
       </c>
       <c r="O19" s="59" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="P19" s="8"/>
     </row>
@@ -3142,13 +3145,13 @@
         <v>92</v>
       </c>
       <c r="M20" s="76" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N20" s="59" t="s">
         <v>202</v>
       </c>
       <c r="O20" s="59" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="66.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3188,27 +3191,27 @@
         <v>92</v>
       </c>
       <c r="M21" s="76" t="s">
+        <v>243</v>
+      </c>
+      <c r="N21" s="59" t="s">
         <v>209</v>
       </c>
-      <c r="N21" s="59" t="s">
-        <v>210</v>
-      </c>
       <c r="O21" s="59" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="66.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="71" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" s="72" t="s">
         <v>211</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="D22" s="72" t="s">
         <v>212</v>
       </c>
-      <c r="D22" s="72" t="s">
+      <c r="E22" s="72" t="s">
         <v>213</v>
-      </c>
-      <c r="E22" s="72" t="s">
-        <v>214</v>
       </c>
       <c r="F22" s="73">
         <v>2</v>
@@ -3225,10 +3228,10 @@
         <v>High</v>
       </c>
       <c r="J22" s="72" t="s">
+        <v>214</v>
+      </c>
+      <c r="K22" s="72" t="s">
         <v>215</v>
-      </c>
-      <c r="K22" s="72" t="s">
-        <v>216</v>
       </c>
       <c r="L22" s="76" t="s">
         <v>92</v>
@@ -3237,24 +3240,24 @@
         <v>76</v>
       </c>
       <c r="N22" s="59" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O22" s="59" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="66.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="72" t="s">
         <v>218</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="D23" s="72" t="s">
         <v>219</v>
       </c>
-      <c r="D23" s="72" t="s">
+      <c r="E23" s="72" t="s">
         <v>220</v>
-      </c>
-      <c r="E23" s="72" t="s">
-        <v>221</v>
       </c>
       <c r="F23" s="73">
         <v>2</v>
@@ -3271,22 +3274,22 @@
         <v>High</v>
       </c>
       <c r="J23" s="72" t="s">
+        <v>221</v>
+      </c>
+      <c r="K23" s="72" t="s">
         <v>222</v>
-      </c>
-      <c r="K23" s="72" t="s">
-        <v>223</v>
       </c>
       <c r="L23" s="76" t="s">
         <v>75</v>
       </c>
       <c r="M23" s="76" t="s">
+        <v>223</v>
+      </c>
+      <c r="N23" s="59" t="s">
         <v>224</v>
       </c>
-      <c r="N23" s="59" t="s">
-        <v>225</v>
-      </c>
       <c r="O23" s="59" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">

--- a/docs/risk/Risk Register/Risk Register V0.9.xlsx
+++ b/docs/risk/Risk Register/Risk Register V0.9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elind\m4-wt\records\docs\risk\Risk Register\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C341170-B9AF-4184-81F8-E6C28839C22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08833DF2-602C-4872-B9D5-80405F5B2379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="250">
   <si>
     <t>8.3 Highest-priority risk — defence</t>
   </si>
@@ -790,9 +790,12 @@
     <t>New at M2 — raised by the architecture baseline (PED §6A.9, DEC-014). M4 review, 17/10/2026: the service stayed active through the RC staging session of 18/10/2026 (docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md), including two restarts (the deploy and the AC-NFR-2.7 check), and recovered after both load runs; availability over a month is not measurable in M4 (AC-NFR-2.5 Not Met).</t>
   </si>
   <si>
+    <t>Closed at M4 — did not materialise</t>
+  </si>
+  <si>
     <t>New at M2 — raised by DEC-010 (PED §6C, §10.8). 
 M3 review, 16/10/2026: observed in the NFR-2.4 load run on staging (15/10/2026, release candidate v3.0-M3-rc, staging cluster civicconnectstaging, M0). 100 concurrent authenticated users for 600 s: 100 logins during the ramp, then 5,835 reads and 900 status transitions in the window (11.04 requests/s), with 0 failed requests and 0 unhandled server errors. The early-warning indicator was not read: the Atlas metrics for 16:30 to 16:42 UTC were not captured, so database load is an estimate of about 40 to 50 ops/s (data baseline s.7 arithmetic), not a measurement against the 70 ops/s trigger. Storage was not checked. Score unchanged (2 × 2): the run is consistent with the estimate but does not measure the ceiling. Context changed: DEC-003 v0.4 leaves production infrastructure undecided, so the free cluster in production is no longer settled; the risk applies to staging now and to production once its cluster is chosen. Next action: capture Atlas operation and storage metrics during the next load run.
-M4 review, 17/10/2026: pending the RC performance runs on staging (NFR-2.4 load run and NFR-2.1 submission timing). Result at the RC (18/10/2026, docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md): the early-warning indicator was reached. During the NFR-2.4 run Atlas reported about 74 ops/s (trigger 70; M0 limit 100) and connections rose from 3 to 53; every request type's tail grew against M3 (read p95 0.87 s against 0.25 s at about 1.8 times M3's request rate). With the per-year reference counter contended (DEF-032), submissions timed out or were lost: NFR-2.4 failed and NFR-2.1 was not met. Partly materialised; a paid or colocated tier is a go-live condition.</t>
+M4 review, 17/10/2026, completed 18/10/2026: result at the RC (18/10/2026, docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md): the early-warning indicator was reached. During the NFR-2.4 run Atlas reported about 74 ops/s (trigger 70; M0 limit 100) and connections rose from 3 to 53; every request type's tail grew against M3 (read p95 0.87 s against 0.25 s at about 1.8 times M3's request rate). With the per-year reference counter contended (DEF-032), submissions timed out or were lost: NFR-2.4 failed and NFR-2.1 was not met. Partly materialised; a paid or colocated tier is a go-live condition.</t>
   </si>
 </sst>
 </file>
@@ -2125,7 +2128,7 @@
       </c>
       <c r="D32" s="20">
         <f>COUNTIFS('Risk Register'!$F$3:$F$30,2,'Risk Register'!$G$3:$G$30,2,'Risk Register'!$M$3:$M$30,"Open*")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="22">
         <f>COUNTIFS('Risk Register'!$F$3:$F$30,3,'Risk Register'!$G$3:$G$30,2,'Risk Register'!$M$3:$M$30,"Open*")</f>
@@ -2188,7 +2191,7 @@
       </c>
       <c r="C38" s="46">
         <f>COUNTIFS('Risk Register'!$I$3:$I$30,"Medium",'Risk Register'!$M$3:$M$30,"Open*")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="30"/>
       <c r="E38" s="30"/>
@@ -2210,7 +2213,7 @@
       </c>
       <c r="C40" s="51">
         <f>SUM(C37:C39)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D40" s="30"/>
       <c r="E40" s="30"/>
@@ -2221,7 +2224,7 @@
       </c>
       <c r="C41">
         <f>COUNTA('Risk Register'!$B$3:$B$30)-C40</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2910,7 +2913,7 @@
         <v>165</v>
       </c>
       <c r="M15" s="65" t="s">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="N15" s="55" t="s">
         <v>166</v>
@@ -3197,7 +3200,7 @@
         <v>209</v>
       </c>
       <c r="O21" s="59" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="66.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
